--- a/target/test-classes/testdata/ProfileData.xlsx
+++ b/target/test-classes/testdata/ProfileData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local\DXC\iot-fe-automation\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Downloads\QA_Automation\s2-selenium\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FB8E1F-12BC-4A21-87AE-DB0A066A76E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5A7FD6-7FBD-4B3E-917B-7E5A04234C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="2620" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile" sheetId="1" r:id="rId1"/>
@@ -88,10 +88,10 @@
     <t>Same as current</t>
   </si>
   <si>
-    <t>Pass@123</t>
-  </si>
-  <si>
     <t xml:space="preserve">New password below min length </t>
+  </si>
+  <si>
+    <t>Pass123#</t>
   </si>
 </sst>
 </file>
@@ -491,7 +491,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -501,7 +501,7 @@
     <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,7 +521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -529,7 +529,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
@@ -541,7 +541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -549,7 +549,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
@@ -559,7 +559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -567,10 +567,10 @@
         <v>21</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>20</v>
@@ -579,15 +579,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>18</v>
@@ -601,11 +601,11 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{60FFF78E-95B8-4FDC-8F90-127EA6B56F98}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{96A80D58-7D1E-4D2C-B9FE-143C97B87C5C}"/>
-    <hyperlink ref="C2" r:id="rId3" xr:uid="{57C0BD98-ED84-4E8C-B5B6-D7A8150F3190}"/>
-    <hyperlink ref="C3" r:id="rId4" xr:uid="{D762D98A-F550-4A2B-8CD1-0969698DB62A}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{13A39C1F-A9CF-4B9B-8DE5-C8A3382DDC5E}"/>
+    <hyperlink ref="C4" r:id="rId1" display="Pass@123" xr:uid="{60FFF78E-95B8-4FDC-8F90-127EA6B56F98}"/>
+    <hyperlink ref="D4" r:id="rId2" display="Pass@123" xr:uid="{96A80D58-7D1E-4D2C-B9FE-143C97B87C5C}"/>
+    <hyperlink ref="C2" r:id="rId3" display="Pass@123" xr:uid="{57C0BD98-ED84-4E8C-B5B6-D7A8150F3190}"/>
+    <hyperlink ref="C3" r:id="rId4" display="Pass@123" xr:uid="{D762D98A-F550-4A2B-8CD1-0969698DB62A}"/>
+    <hyperlink ref="C5" r:id="rId5" display="Pass@123" xr:uid="{13A39C1F-A9CF-4B9B-8DE5-C8A3382DDC5E}"/>
     <hyperlink ref="D2" r:id="rId6" xr:uid="{70CD444D-0392-461D-B663-41BA138AC1C7}"/>
     <hyperlink ref="D5" r:id="rId7" xr:uid="{B2CC73C0-6B65-4110-A230-233CF91A0ECF}"/>
   </hyperlinks>
